--- a/minio-report-tracker/xlxs/qa1-java21.xlsx
+++ b/minio-report-tracker/xlxs/qa1-java21.xlsx
@@ -801,12 +801,12 @@
   <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -905,7 +905,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22-August-2025</t>
+          <t>29-August-2025</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -987,7 +987,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22-August-2025</t>
+          <t>29-August-2025</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>535</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>591</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>22-August-2025</t>
+          <t>29-August-2025</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>146</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>22-August-2025</t>
+          <t>29-August-2025</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>22-August-2025</t>
+          <t>29-August-2025</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>22-August-2025</t>
+          <t>29-August-2025</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1397,7 +1397,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1529,7 +1529,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>537</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>166</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1793,7 +1793,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25-August-2025</t>
+          <t>01-September-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
